--- a/data/trans_orig/P3A$yo-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A$yo-Estudios-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W44"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según quién se ocupa principalmente de las tareas domésticas (multirrespuesta) en 2023</t>
+          <t>Hogares según quién se ocupa principalmente de las tareas domésticas (multirrespuesta) en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266844</t>
+          <t>268785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>308711</t>
+          <t>310912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>624677</t>
+          <t>625679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>656181</t>
+          <t>656571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>903045</t>
+          <t>903201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>954901</t>
+          <t>956313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>218024</t>
+          <t>216944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258967</t>
+          <t>257615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64450</t>
+          <t>63656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90242</t>
+          <t>89704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287633</t>
+          <t>286533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339603</t>
+          <t>335837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85784</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68558</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>104874</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>183</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>122795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>191529</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>218710</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -1054,112 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57719</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>70118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>237</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115795</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>101652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>130175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>331</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>173514</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>193177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -1167,112 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85784</t>
+          <t>25224</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69813</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105301</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>105745</t>
+          <t>50483</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90836</t>
+          <t>40558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122950</t>
+          <t>60248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>140</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>191529</t>
+          <t>75707</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169779</t>
+          <t>63428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213672</t>
+          <t>90037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1280,112 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30718</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22635</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>41168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61573</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>72990</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>181</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79797</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>106914</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1393,225 +1393,229 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57719</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47714</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69533</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>115795</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102484</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130389</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>173514</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156352</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196323</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25224</t>
+          <t>1354415</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>929677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34362</t>
+          <t>1536495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>2101599</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41548</t>
+          <t>2063978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62746</t>
+          <t>2136282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>75707</t>
+          <t>3456014</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63454</t>
+          <t>2829615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>3702192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -1619,112 +1623,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>968519</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>650080</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41385</t>
+          <t>1102830</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>743</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61573</t>
+          <t>475220</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51306</t>
+          <t>352565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72901</t>
+          <t>547866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>1443739</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>1150022</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107952</t>
+          <t>1611417</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -1732,229 +1736,225 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>499</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>658291</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>443390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>760875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>741</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>578627</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>440052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>668458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>1236918</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>1011334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>1401766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1354415</t>
+          <t>43934</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>959061</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1533206</t>
+          <t>66506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2101599</t>
+          <t>28218</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2064642</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2142768</t>
+          <t>38971</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>105</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3456014</t>
+          <t>72152</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2863376</t>
+          <t>53908</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3686542</t>
+          <t>95609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1962,112 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>968519</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>676480</t>
+          <t>19870</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1101577</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475220</t>
+          <t>30806</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>338098</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>548000</t>
+          <t>42991</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1443739</t>
+          <t>63047</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1145531</t>
+          <t>45274</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1614566</t>
+          <t>81569</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2075,112 +2075,112 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>27673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36482</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>50522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2188,225 +2188,229 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>263124</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17222</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>936382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270941</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1058480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n"/>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>658291</t>
+          <t>470459</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>435504</t>
+          <t>445163</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>762945</t>
+          <t>492993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>933</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>578627</t>
+          <t>597713</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>404574</t>
+          <t>578385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>663688</t>
+          <t>612140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1236918</t>
+          <t>1068172</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>989084</t>
+          <t>1034284</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1391707</t>
+          <t>1096074</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -2414,112 +2418,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>391</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345493</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320237</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>374625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>214905</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>192914</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>234769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>718</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>560398</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>527803</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>594436</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>45,48%</t>
         </is>
       </c>
     </row>
@@ -2527,112 +2531,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>43934</t>
+          <t>164805</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>140532</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65780</t>
+          <t>192167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>228</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28218</t>
+          <t>168424</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>145938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>190090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>380</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>72152</t>
+          <t>333230</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53987</t>
+          <t>302053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94741</t>
+          <t>365875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -2640,112 +2644,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49119</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>63047</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84548</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2753,112 +2757,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>37586</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27560</t>
+          <t>51515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>115</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>78792</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26323</t>
+          <t>64603</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48346</t>
+          <t>93841</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -2866,342 +2870,342 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>263124</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>870343</t>
+          <t>20408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>270941</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1007990</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>470459</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>445741</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>494959</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>597713</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>578951</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>612086</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1068172</t>
+          <t>23101</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1035817</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1098824</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n"/>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>345493</t>
+          <t>2113420</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>316753</t>
+          <t>1604062</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>372419</t>
+          <t>2294315</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>214905</t>
+          <t>3340694</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>195177</t>
+          <t>3296788</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238884</t>
+          <t>3393953</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>560398</t>
+          <t>5454113</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>526529</t>
+          <t>4807089</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>595028</t>
+          <t>5688597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>
@@ -3209,112 +3213,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1552098</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1174071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1690838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>765059</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>615246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>832941</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2317157</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2033941</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>2470658</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -3322,112 +3326,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>753</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>908880</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700755</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1005290</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>852796</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>704897</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>928762</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1761676</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1541657</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1889266</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -3435,112 +3439,112 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>164805</t>
+          <t>105125</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141528</t>
+          <t>79632</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>191468</t>
+          <t>129356</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>168424</t>
+          <t>146251</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>148377</t>
+          <t>120665</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189939</t>
+          <t>167421</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>445</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>333230</t>
+          <t>251375</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>302152</t>
+          <t>219208</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>365482</t>
+          <t>289454</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -3548,112 +3552,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95050</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72545</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>119048</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>225</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122496</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99700</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>142070</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>347</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217547</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>185505</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>249387</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -3661,112 +3665,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>57508</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>74768</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>174</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>66077</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>98746</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>140020</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>118688</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>162320</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3774,1477 +3778,117 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>277420</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>31440</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51376</t>
+          <t>1081488</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>41207</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52029</t>
+          <t>39668</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>78792</t>
+          <t>304014</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>64396</t>
+          <t>56275</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>94230</t>
+          <t>1122374</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n"/>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>8669</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>4052</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>22854</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>2579</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>6355</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>11248</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>6017</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>24948</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n"/>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Otra situación</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>8645</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>18044</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>14457</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>7572</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>25547</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>23101</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>14425</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>36594</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Yo</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2113420</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>1664012</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2299139</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>61,24%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>66,63%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>3340694</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>3293300</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>3396277</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>91,46%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>7142</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>5454113</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>4762116</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>5697745</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>76,78%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>67,04%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Mi pareja</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>1552098</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1215714</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1696844</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>35,23%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>49,17%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>765059</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>617497</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>835390</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>22,87%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>2972</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>2317157</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>2029413</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>2472143</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>28,57%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>34,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Mi pareja y yo</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>1566</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no es mi pareja y yo</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1566</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona del hogar</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>908880</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>720533</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1007774</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>852796</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>696429</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>929429</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>23,35%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>25,45%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>1761676</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>1531790</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>1895755</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>26,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Una persona contratada para ello</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>1566</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>105125</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>78727</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>127369</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>146251</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>118207</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>167507</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>251375</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>215396</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>283559</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>95050</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>73624</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>119017</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>122496</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>100259</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>144146</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>217547</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>183179</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>247055</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>57508</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>43497</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>74005</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>82512</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>66697</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>98527</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>140020</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>118476</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>163113</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Otra situación</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>277420</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>29773</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>970908</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>28,14%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>26594</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>17077</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>40164</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>304014</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>54927</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>1144948</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
@@ -5253,13 +3897,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A34:A43"/>
-    <mergeCell ref="A4:A13"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A25:A31"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A14:A23"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A11:A17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/P3A$yo-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A$yo-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>288546</t>
+          <t>325784</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>268785</t>
+          <t>302427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>310912</t>
+          <t>348613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>641382</t>
+          <t>698660</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>625679</t>
+          <t>681969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>656571</t>
+          <t>714918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>929928</t>
+          <t>1024444</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>903201</t>
+          <t>995278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>956313</t>
+          <t>1054637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>238085</t>
+          <t>269375</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216944</t>
+          <t>246980</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257615</t>
+          <t>291648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74934</t>
+          <t>80640</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63656</t>
+          <t>69430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89704</t>
+          <t>96124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>313019</t>
+          <t>350015</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286533</t>
+          <t>321368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335837</t>
+          <t>377075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85784</t>
+          <t>94132</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68558</t>
+          <t>77829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104874</t>
+          <t>113512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105745</t>
+          <t>116165</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92661</t>
+          <t>99250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122795</t>
+          <t>132507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>191529</t>
+          <t>210298</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>171619</t>
+          <t>190088</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>218710</t>
+          <t>235892</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57719</t>
+          <t>60662</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46574</t>
+          <t>49793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70118</t>
+          <t>74130</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>115795</t>
+          <t>123036</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101652</t>
+          <t>109327</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130175</t>
+          <t>139366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>173514</t>
+          <t>183698</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156426</t>
+          <t>166514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193177</t>
+          <t>204055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25224</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18029</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33861</t>
+          <t>37118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>54869</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40558</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60248</t>
+          <t>66202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>75707</t>
+          <t>82054</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63428</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90037</t>
+          <t>96628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22635</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41168</t>
+          <t>43520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61573</t>
+          <t>65227</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51514</t>
+          <t>55551</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72990</t>
+          <t>77691</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>97740</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79797</t>
+          <t>83105</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>106914</t>
+          <t>113569</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17200</t>
+          <t>19791</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1354415</t>
+          <t>1461796</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>929677</t>
+          <t>1405871</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1536495</t>
+          <t>1509290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2101599</t>
+          <t>2017501</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2063978</t>
+          <t>1981361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2136282</t>
+          <t>2043463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3456014</t>
+          <t>3479297</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2829615</t>
+          <t>3414702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3702192</t>
+          <t>3538790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>968519</t>
+          <t>1078680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>650080</t>
+          <t>1025435</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1102830</t>
+          <t>1131674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>475220</t>
+          <t>517731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>352565</t>
+          <t>481597</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>547866</t>
+          <t>552899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1443739</t>
+          <t>1596411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1150022</t>
+          <t>1528205</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1611417</t>
+          <t>1657934</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>658291</t>
+          <t>694053</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>443390</t>
+          <t>636609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>760875</t>
+          <t>749343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>578627</t>
+          <t>648717</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>440052</t>
+          <t>607010</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>668458</t>
+          <t>694317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1236918</t>
+          <t>1342770</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1011334</t>
+          <t>1276328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1401766</t>
+          <t>1413962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -1859,69 +1859,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>43934</t>
+          <t>42531</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66506</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>31977</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>23827</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>41642</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>1,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28218</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>19584</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38971</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>105</t>
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>72152</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53908</t>
+          <t>60654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95609</t>
+          <t>91991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>36047</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>35723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42991</t>
+          <t>46273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>63047</t>
+          <t>71770</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>45274</t>
+          <t>56171</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>81569</t>
+          <t>90058</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>20435</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27673</t>
+          <t>28875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>39790</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>29783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50522</t>
+          <t>52350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>263124</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>936382</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,67 +2233,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>33600</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>22307</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>50911</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>270941</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>22477</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1058480</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>470459</t>
+          <t>514603</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>445163</t>
+          <t>487830</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>492993</t>
+          <t>540067</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>597713</t>
+          <t>663039</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>578385</t>
+          <t>644181</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>612140</t>
+          <t>677799</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1068172</t>
+          <t>1177642</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1034284</t>
+          <t>1145388</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1096074</t>
+          <t>1213431</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>345493</t>
+          <t>385234</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>320237</t>
+          <t>355763</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>374625</t>
+          <t>413348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>214905</t>
+          <t>231777</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>192914</t>
+          <t>209987</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>234769</t>
+          <t>255412</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>560398</t>
+          <t>617011</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>527803</t>
+          <t>581765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>594436</t>
+          <t>658700</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>164805</t>
+          <t>183423</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140532</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192167</t>
+          <t>212270</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>168424</t>
+          <t>182299</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145938</t>
+          <t>160001</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>190090</t>
+          <t>206414</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>333230</t>
+          <t>365721</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302053</t>
+          <t>330774</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>365875</t>
+          <t>404618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>52518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,17 +2802,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41207</t>
+          <t>45862</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>36054</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51515</t>
+          <t>57776</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>78792</t>
+          <t>85699</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64603</t>
+          <t>70391</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93841</t>
+          <t>103694</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,17 +2915,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>30390</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27170</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>25480</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36332</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2113420</t>
+          <t>2302183</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1604062</t>
+          <t>2239892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2294315</t>
+          <t>2364467</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3340694</t>
+          <t>3379200</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3296788</t>
+          <t>3342360</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3393953</t>
+          <t>3417286</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5454113</t>
+          <t>5681383</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4807089</t>
+          <t>5603862</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5688597</t>
+          <t>5759016</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1552098</t>
+          <t>1733290</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1174071</t>
+          <t>1666500</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1690838</t>
+          <t>1799797</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>765059</t>
+          <t>830148</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>615246</t>
+          <t>791284</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>832941</t>
+          <t>872626</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2317157</t>
+          <t>2563438</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2033941</t>
+          <t>2485991</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2470658</t>
+          <t>2646137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>908880</t>
+          <t>971608</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>700755</t>
+          <t>905855</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1005290</t>
+          <t>1033129</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>852796</t>
+          <t>947181</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>704897</t>
+          <t>893196</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>928762</t>
+          <t>1000612</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1761676</t>
+          <t>1918789</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1541657</t>
+          <t>1835780</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1889266</t>
+          <t>1998505</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -3449,67 +3449,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>79632</t>
+          <t>91221</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>129356</t>
+          <t>130767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>157969</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>139917</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>177589</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>146251</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>120665</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>167421</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>251375</t>
+          <t>264718</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>219208</t>
+          <t>240726</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>289454</t>
+          <t>296122</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>95050</t>
+          <t>103069</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>72545</t>
+          <t>84100</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119048</t>
+          <t>126313</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>122496</t>
+          <t>136454</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>99700</t>
+          <t>119342</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142070</t>
+          <t>156596</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>217547</t>
+          <t>239523</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>185505</t>
+          <t>215051</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>249387</t>
+          <t>270596</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>48451</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74768</t>
+          <t>78347</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66077</t>
+          <t>74298</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>98746</t>
+          <t>101584</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>150367</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>118688</t>
+          <t>132556</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>162320</t>
+          <t>174006</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>277420</t>
+          <t>37304</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1081488</t>
+          <t>53004</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>304014</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>56275</t>
+          <t>54061</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1122374</t>
+          <t>92244</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
